--- a/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SKM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>SKM</t>
   </si>
@@ -656,542 +656,555 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2814800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2885500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2998700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2831800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3205900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3024200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3054000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3450600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3209300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3329500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3513200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3270500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3269600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3353300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3295800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3170700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3260300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3293500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3221500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3161300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3093900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3043700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>12065800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3643200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3728700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3738500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3746400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4059500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3904600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3944800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3655400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3391000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3489600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3512500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3957600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3909600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3824100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3810900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3917000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>3819400</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>248200</v>
+      </c>
+      <c r="E9" s="3">
         <v>279400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3492600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>330000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>275500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>291000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1054000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>355700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>291500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>323200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>871300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>303400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>291300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>317000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>120500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>131400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>140800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>145800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>141200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>138100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>137400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>143500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>578000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>155100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>167900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>163800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>162600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>163700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>165200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>172300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>136400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>171900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>183800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>180600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>190800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>197200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>187500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>199000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>153400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>238000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2566600</v>
+      </c>
+      <c r="E10" s="3">
         <v>2606100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-493900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2501800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2930400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2733300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2000000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3094900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2917800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3006200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2641900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2967100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2978300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3036200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3175400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3039300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3119500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3147600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3080300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3023100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2956500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2900200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>11487800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3488100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3560800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3574700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3583800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3895800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3739400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3772400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3519000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3219100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3305800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3331900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3766900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>3712400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>3636700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3612000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>3763600</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>3581400</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1234,130 +1247,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E12" s="3">
         <v>56900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>235200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>69900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>59100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>61100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>255900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>78000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>70700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>66200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>90600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>67200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>66700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>56400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>67100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>61800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>67400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>60100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>75800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>60300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>62000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>61800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>264900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>80700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>85000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>92700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>86500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>83300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>84700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>90800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>88900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>76200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>82500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>75100</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>90300</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>90800</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>83500</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>85200</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>82100</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>76900</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1478,252 +1495,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-6400</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-66700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-3200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>50700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>72900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-14500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-47900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>12500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>300</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="V14" s="3">
         <v>2400</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>4000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>150500</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>10300</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>54900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>214000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>400</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>800</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>52300</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>300</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>3700</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>2000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>5700</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>542600</v>
+      </c>
+      <c r="E15" s="3">
         <v>556100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2401900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>618400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>639300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>588900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>536700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>675500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>641400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>667600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>698800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>664700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>693700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>690400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>676400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>657900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>689600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>701400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>691800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>696100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>684800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>672700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2748500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>775500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>807500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>827200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>912300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>856100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>818700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>810900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>676100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>621700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>644900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>660200</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>696900</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>684300</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>674200</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>685500</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>695000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>659700</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1763,252 +1789,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2448000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2533100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2916200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2796900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2957700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2639600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2881900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3045100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2819900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2959600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3283400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2902100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2918400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2975200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3117500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2831100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2911000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2960500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3055700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2866500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2797100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2766800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>11279900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3367600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3449200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3485400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3664800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3790900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3622600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3651300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3680200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3145000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3200300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3239800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3736700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3564600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3455400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3443500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3650900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3442500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>366800</v>
+      </c>
+      <c r="E18" s="3">
         <v>352400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>82500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>34800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>248100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>384700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>172100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>405600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>389400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>369900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>229800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>368300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>351200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>378100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>178400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>339600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>349300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>332900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>165800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>294800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>296800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>276900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>785900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>275700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>279500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>253100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>81700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>268600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>282000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>293500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-24700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>246000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>289300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>272600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>220900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>345000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>368800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>367500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>266100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>376900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2051,618 +2084,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="E20" s="3">
         <v>9400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-121600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>106900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>26000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-391800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>10900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>20300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-19900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>14500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-24200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>109100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>27800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>188000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>133700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>109700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>265700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>320200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>140700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>130200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>116400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>225300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>607100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>866100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>748000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>552300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>662700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>601900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>355900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>351300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>307600</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>78400</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>939800</v>
+      </c>
+      <c r="E21" s="3">
         <v>899100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2606000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>546400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>861500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>970800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1100500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1080800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1039400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1032300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>929900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1022100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1040400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1048100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>886300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1001200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1078700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1037300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1019100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1111900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1261900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1175500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4023100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1338100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1435000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1250100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>956400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1291600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1253400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1367100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1293500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1766000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1714900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1517100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1615900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1665600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1432300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1434000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1295900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1143300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>55100</v>
+      </c>
+      <c r="E22" s="3">
         <v>58900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>265500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>69300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>70200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>66300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>272900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>74200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>71900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>78200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>79700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>72500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>72800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>71400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>77200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>55200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>57700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>56900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>53600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>53300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>51600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>50600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>216700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>143600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>155100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>84400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>89700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>87900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>87600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>93100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>75000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>57500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>60400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>63100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>68300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>63400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>66100</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>67000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>66000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>369400</v>
+      </c>
+      <c r="E23" s="3">
         <v>305900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>95500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-116600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>177600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>344900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>323600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>277700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>347000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>327900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>167600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>297200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>341500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>322800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>108000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>264500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>306100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>251800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>221200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>269300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>433200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>360000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>678900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>397800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>444700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>309400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>311000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>310800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>425700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>507400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1054600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>977000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>761900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>815400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>883600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>658600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>651800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>507700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>388100</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E24" s="3">
         <v>98000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>28300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>116100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>99300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>56400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>64400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>92900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>58600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>23100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>68200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>77500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>90800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-59800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>85200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>109900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>82100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>62700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>71700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>102700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>96700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>165900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>96100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>94500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>52400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>31400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>66700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>82900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>85700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>108800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>204200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>208900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>179400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>234000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>185800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>112600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>126700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>80500</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2783,252 +2832,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>300900</v>
+      </c>
+      <c r="E26" s="3">
         <v>207900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>67200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-118700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>61500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>245500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>267200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>213300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>254100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>269300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>144500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>229000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>264000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>232000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>167800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>179300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>196200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>169700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>158600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>197600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>330500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>263300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>513000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>301700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>350200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>257000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-39400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>244200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>228000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>340000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>398600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>850400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>768000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>582400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>581400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>697800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>546000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>525100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>427200</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>289900</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>211800</v>
+        <v>300700</v>
       </c>
       <c r="E27" s="3">
+        <v>208500</v>
+      </c>
+      <c r="F27" s="3">
         <v>64200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-116100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>62600</v>
       </c>
-      <c r="H27" s="3">
-        <v>247500</v>
-      </c>
       <c r="I27" s="3">
+        <v>244100</v>
+      </c>
+      <c r="J27" s="3">
         <v>183500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>201000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>241300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>259000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>131900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>217600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>247100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>220000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>156700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>168600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>190100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>159800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>141700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>189900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>313600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>253300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>475400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>292100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>343200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>256100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-27200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>240900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>228500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>341700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>404200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>832400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>762900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>583800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>511800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>700300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>542500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>530200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>432400</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3149,8 +3207,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3193,8 +3254,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>91</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>91</v>
@@ -3205,29 +3266,29 @@
       <c r="T29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="V29" s="3">
         <v>80000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>395400</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>257900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>157000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>641800</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
@@ -3271,8 +3332,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3393,8 +3457,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3515,252 +3582,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-9400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>121600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-106900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-26000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>391800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-10900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-20300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>19900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-14500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>24200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-109100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-27800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-188000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-133700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-109700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-265700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-320200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-140700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-130200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-116400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-225300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-607100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-866100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-748000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-552300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-662700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-601900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-355900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-351300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-307600</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-78400</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>303900</v>
+      </c>
+      <c r="E33" s="3">
         <v>211800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>77900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-112600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>66200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>247500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>196900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>204700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>244900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>262700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>135700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>221300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>249900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>222800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>156700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>168600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>190100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>159800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>221700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>585400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>571600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>410400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1117200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>292100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>343200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>256100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-27200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>240900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>228500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>341700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>404200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>832400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>762900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>583800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>511800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>700300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>542500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>530200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>432400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3881,257 +3957,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>303900</v>
+      </c>
+      <c r="E35" s="3">
         <v>211800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>77900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-112600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>66200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>247500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>196900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>204700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>244900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>262700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>135700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>221300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>249900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>222800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>156700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>168600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>190100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>159800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>221700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>585400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>571600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>410400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1117200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>292100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>343200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>256100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-27200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>240900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>228500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>341700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>404200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>832400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>762900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>583800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>511800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>700300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>542500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>530200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>432400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4174,8 +4259,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4218,1106 +4304,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>777400</v>
+      </c>
+      <c r="E41" s="3">
         <v>968800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1032200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>985700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1738700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1559900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1369900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1497100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1141900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1279100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1122000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>864900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1182900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1300700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1411700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>869800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>876200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>688900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>654500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1118700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1154500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>911200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1027200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1450500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1212500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>938900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1080200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1147800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1277400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1871900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1265600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2238500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1508800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1584000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1282800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1273500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1089100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1418400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1354700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>773300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>537700</v>
+      </c>
+      <c r="E42" s="3">
         <v>195800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>66800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>214300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>148800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>172900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>165400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>206100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>159600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>263900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>166100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>320100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>269700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>170500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>118300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>472700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>523300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>378500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>325600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1264900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1186400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1078700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1109500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>840400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>795000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>903200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>766900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>866400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>728100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>733100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>975400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>318100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>452600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>540900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>590800</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>626300</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>647200</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>612800</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>437300</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>580900</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1568900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1688600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1703700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1876800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1883600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1734200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1701900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1974800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1836300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1897100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1920900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2006600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1790200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1884400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1960600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2052200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2083500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2117900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1957700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2772400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2584400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2644400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2528400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2663000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2649400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2902000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2886300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3122000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2860700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3116800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2605400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3040500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2736500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3179400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3039200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2826800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2900700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2901300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3081700</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>3293200</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>96300</v>
+      </c>
+      <c r="E44" s="3">
         <v>132700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>116100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>160200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>142600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>139800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>142000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>169300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>154700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>156500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>138700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>139200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>126600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>153500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>124800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>143500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>139300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>172000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>153500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>148700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>158800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>163900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>128600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>166300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>165500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>174800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>138400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>178500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>197000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>239900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>242000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>208700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>217800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>213800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>239700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>219000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>231900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>223700</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>233900</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>246600</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>228000</v>
+      </c>
+      <c r="E45" s="3">
         <v>218600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1690000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>176500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>180700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>216200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1638700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>255400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>250600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>208800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1675700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1521300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>216000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>336400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1799000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1804400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1744200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1682200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1673200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1685000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1771500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1762000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1787600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1834500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1869300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1904400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2003300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1881800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1612400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1635700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1597000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1505000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1648400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1597800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>305100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>341700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>228600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>212400</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>289400</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>305900</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>4652900</v>
+      </c>
+      <c r="E46" s="3">
         <v>4675600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4660200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4932100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5562500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5172400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5061200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5608100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4978700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5284500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5078500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4913600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5087400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5373300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5414400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5342600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5366500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5039500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4764500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6989700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6855700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6560200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6581300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6954700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6691700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6823200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6875200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7196700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6675700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7597400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6685400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7310800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6564000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7115900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5457600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5287300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>5097500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>5368600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>5397000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>5199900</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>5299600</v>
+      </c>
+      <c r="E47" s="3">
         <v>3652100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3759600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2937800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2941600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2839100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2856500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2705000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2687900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2809100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2771800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2678500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2679100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2633400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2823200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2756600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2913200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3235400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3194500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>15039700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13968200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12464800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12336800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12316200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12493000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12472300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>12502800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>12994600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>12402900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>12830400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>11621100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>10715900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>10427800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>9560700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>9483000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>8899800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>8030500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>7602200</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>7603200</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>7518000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>7246400</v>
+      </c>
+      <c r="E48" s="3">
         <v>7455400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8249100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8484400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8808100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8136500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8547100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9225600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8947900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9391300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10037800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9401300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9813700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9833400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10010700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9104400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9648000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9698000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9670700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9855200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9932800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9546300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10032800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9386500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10160800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10069700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10993400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>10310700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9942300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>10188200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9003400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7678300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8009300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8104800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8927500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8449400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>8424900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>8936000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>9336800</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>8818900</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>2223100</v>
+      </c>
+      <c r="E49" s="3">
         <v>2379900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2620700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2734100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2947100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2815400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2888700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3367400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3337100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3560700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3806500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3665700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3867500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4016700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4049900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3968600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4254900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4434400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4456700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5635200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5629100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5622000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5845300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6083200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6545900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>6426000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>6643300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7011600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7117600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7518000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>7099700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4170600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4448600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4511000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4841700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>4934900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>5000900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>5037500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>5137900</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>4591200</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5438,8 +5552,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5560,130 +5677,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>1492700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1532900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>657900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1448600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1366500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1329500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>538300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1485400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1376800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1465900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>670500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>716100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1526000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1530700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1182900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1114600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1110200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1135100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1097000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1238200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1157300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1150100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1134000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1186500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1333900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1439300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1407300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1632000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1341300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1311200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1180300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1055500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1073200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1060500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>707400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>521500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>530700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>521800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>693000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>472200</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5804,130 +5927,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>20941500</v>
+      </c>
+      <c r="E54" s="3">
         <v>19722700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20857200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>20569000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21652700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20317200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20656800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22439900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21372800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>22543100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23226500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>22195800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23009700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>23422300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>23481200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22286700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>23292800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>23542500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>23183500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>38758100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>37543200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>35343500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>35930200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>35927000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>37225300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>37230600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>38422000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>39145600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>37479700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>39445300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>35590100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>30931100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>30522900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>30352900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>29417200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>28093000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>27084400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>27466000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>28167900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>26600100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5970,8 +6099,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -6014,740 +6144,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>75900</v>
+      </c>
+      <c r="E57" s="3">
         <v>135000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>76800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>137000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>99000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>79300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>85600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>126000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>67400</v>
-      </c>
-      <c r="L57" s="3">
-        <v>107900</v>
       </c>
       <c r="M57" s="3">
         <v>107900</v>
       </c>
       <c r="N57" s="3">
+        <v>107900</v>
+      </c>
+      <c r="O57" s="3">
         <v>94800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>77200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>106600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>66900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>108600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>86000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>116300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>142900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>253700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>228200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>249000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>279700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>285700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>300500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>327300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>372600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>405200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>332700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>283700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>320300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>217500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>221100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>204600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>309500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>226300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>219400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>237100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>362200</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>276000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>1077500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1120000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1150300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1445600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1769800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2152400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1970900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2527000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2131100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1996200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1538200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1232100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1747900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2127500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1872800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2070200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1920500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1409000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1344700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1420900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1244900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1236100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1056900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1029100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>963600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1234000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1198200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1223800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1310400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1605600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>894000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1002000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>856100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1192300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1461600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1452600</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1315500</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>944800</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>802000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>615100</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>1799800</v>
+      </c>
+      <c r="E59" s="3">
         <v>1947300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2363900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1852600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2440400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2844700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3156900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2406500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1952900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2398900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2637100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2406000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2169000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2298100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4095200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3244300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3751200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3814800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3732700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4610800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4393200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4508600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4796900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4594700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4758600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4813200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5103100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4927800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4464800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>5319400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4537700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3551200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3760600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4385500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4484900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3942300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3822900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>4448200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>4635500</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>3962700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>3776000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3999900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4523500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4621500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5382700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5928400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6244200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6188000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5135100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5400800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5393400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4848000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5056000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5524300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6034900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5423100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5757700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5340200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5220300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6285400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5866300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5993700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6133500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5909400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6022700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6374500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6673900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6556800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6107900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7208600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5751900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4770700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4837800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5782300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>6256000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>5621200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>5357800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>5630000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>5799700</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>4853900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>5534600</v>
+      </c>
+      <c r="E61" s="3">
         <v>5650400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6035900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6526100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6403500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5339800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5316200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5490100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5711200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6422800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6678600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6522300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6844600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6729300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6440900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5995600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6304100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6669800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6431400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8165900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8169800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7876200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8059700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7920900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8322200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8551200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8623500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8522600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7920200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8288300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7213600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5575400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5547400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5319600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5111100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5104400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5178200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5654600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5830800</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5840500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>348600</v>
+      </c>
+      <c r="E62" s="3">
         <v>353900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>244100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>354100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>331200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>299400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>470600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>571200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>759700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>779300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1038900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>997600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1072500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1076600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1889000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1891200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1999600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2085000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2280300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3919000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3702000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3292500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3439900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3368000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3426800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3363300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3730200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3901800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3713300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3819900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3851200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2626500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2574400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2461100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2184400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1988400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1874200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1860200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2032600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1915900</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6868,8 +7017,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6990,8 +7142,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -7112,130 +7267,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>10935700</v>
+      </c>
+      <c r="E66" s="3">
         <v>10954100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11882400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12162900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12807100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12208200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12650300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12875900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12238800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13277000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13796600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13005600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13599700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13976100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14992500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13887800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14660500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14683200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14498900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19056700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>18415600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17659600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>18122300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17605800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>18193000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>18168300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>18914300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>18899300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>17654900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19205500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16714600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13198100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13130700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13728400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>13716100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>12834200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>12499800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>13239200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>13793600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>12760400</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7278,8 +7439,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7400,8 +7562,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7522,8 +7687,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7644,8 +7812,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7766,130 +7937,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>16285800</v>
+      </c>
+      <c r="E72" s="3">
         <v>16381000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15890500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16241200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17034600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15677100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15553300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>17451400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16567800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16911400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17582300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16958200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17244300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17294500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16847800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16393600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17006300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>17168800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>16828000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>16730300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>16259600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>16928100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>17236400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>17398700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18050600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18362200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>18894400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19871700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19470600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19870500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>18601400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>17574500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>17434000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>16667600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>15695600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>15173300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>14531800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>14306000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>14357800</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>13922500</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -8010,8 +8187,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -8132,8 +8312,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8254,130 +8437,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>9968100</v>
+      </c>
+      <c r="E76" s="3">
         <v>8727400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8910900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8330100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8757300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8025800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7919200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8940700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8548300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8674600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8782700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8579600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8796100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8837600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8488700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8398900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8632300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8859300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8684500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19701400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19127600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17683900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17807900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>18321200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>19032300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>19062300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>19507700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>20246300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>19824800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>20239800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>18875500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>17732900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>17392200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>16624500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>15701100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>15258700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>14584600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>14226800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>14374300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>13839700</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8498,257 +8687,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>303900</v>
+      </c>
+      <c r="E81" s="3">
         <v>211800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>77900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-112600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>66200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>247500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>196900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>204700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>244900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>262700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>135700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>221300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>249900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>222800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>156700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>168600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>190100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>159800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>221700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>585400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>571600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>410400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1117200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>292100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>343200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>256100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-27200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>240900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>228500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>341700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>404200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>832400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>762900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>583800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>511800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>700300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>542500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>530200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>432400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>292600</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8791,130 +8989,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>661300</v>
+      </c>
+      <c r="E83" s="3">
         <v>609100</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="F83" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>702000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>666400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>693100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>560400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>689300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>719900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>716600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>575500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>199500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>726100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>779000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>701100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>681500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>715000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>728600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>744200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>789300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>777100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>764800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3127500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>796700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>835300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>856200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>874600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>892700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>855000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>848400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>711200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>653900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>677500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>692100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>732200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>718700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>707600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>715200</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>722200</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>688100</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -9035,8 +9237,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -9157,8 +9362,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9279,8 +9487,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9401,8 +9612,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9523,130 +9737,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>779700</v>
+      </c>
+      <c r="E89" s="3">
         <v>699100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>762800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>118400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1037700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>850200</v>
       </c>
-      <c r="I89" s="3" t="s">
+      <c r="J89" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1086900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>921700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>832400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>936100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>992100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1042400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>786000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1027400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>768900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1095600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>996900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1011600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1053900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1039700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>659400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4366400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1263500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1549000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>816800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>975700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>746100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>907500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>881500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1389100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>382000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1024900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>829300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>828600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>969400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>776500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>837300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1379600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>799200</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9689,130 +9909,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-289700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-237300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-512400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-449100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-217000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-368200</v>
       </c>
-      <c r="I91" s="3" t="s">
+      <c r="J91" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-375000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-375900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-429000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-707800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-488500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-472100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-595700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-872521000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-858866000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-556669000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-758367000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1082665000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-888446000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-415900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-558800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2668400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-742400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-526800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-878200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-969100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-796300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-571500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-629400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-789700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-622200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-383600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-527100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-730500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-688700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-391900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-608900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1158400</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-855700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9933,8 +10157,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -10055,130 +10282,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-710000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-313400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-285700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-706800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>97400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-314900</v>
       </c>
-      <c r="I94" s="3" t="s">
+      <c r="J94" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-425200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-259200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-478900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-588700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-674000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-682700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-600600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-335700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-566700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-595300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-616500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-583300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-874100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-764500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-387600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3187800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-907100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-515500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1035700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1309800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1016400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-404700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-400100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2284100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-292400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-356000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-456800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-845900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-805200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-473600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-590600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-755400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-667600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -10221,8 +10454,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -10253,11 +10487,11 @@
       <c r="L96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N96" s="3">
         <v>103400</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="O96" s="3" t="s">
         <v>91</v>
@@ -10265,39 +10499,39 @@
       <c r="P96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R96" s="3">
         <v>-135700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-132100</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
-        <v>-133400</v>
+        <v>0</v>
       </c>
       <c r="V96" s="3">
         <v>-133400</v>
       </c>
       <c r="W96" s="3">
-        <v>0</v>
+        <v>-133400</v>
       </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-556600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-56300</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -10305,11 +10539,11 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-64000</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -10317,11 +10551,11 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-57200</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
@@ -10329,11 +10563,11 @@
         <v>0</v>
       </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-62100</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
         <v>0</v>
       </c>
@@ -10341,10 +10575,13 @@
         <v>0</v>
       </c>
       <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-63500</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10465,8 +10702,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10587,8 +10827,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10709,370 +10952,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-238500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-400900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-403700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-105700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1082400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-350100</v>
       </c>
-      <c r="I100" s="3" t="s">
+      <c r="J100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-357300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-771000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-161500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-118700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-612300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-464800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-330200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-164700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-182000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-309700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-364600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-892500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-220900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-43900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-377800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1093200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-56600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-725800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>83100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>324500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>120000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1033500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>19100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-163300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>696800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-746200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-13300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>30200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>19200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-603000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-177800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-48400</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-343800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="F101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>7500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>5700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-8800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>7900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>5600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>5300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>7200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>6100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1100</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>2300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>5600</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-170700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>76100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-689400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>41300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>185700</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>299100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-105600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>196400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>224200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-292500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-104700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-142900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>518100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>28100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>196300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>16900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-464100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-35800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>231000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-102400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>74100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>297900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>307100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-128600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-16100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-144100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-532800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>500800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1055800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>783600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-75200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>359500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>9300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>184400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-297700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>63700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>581400</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-216300</v>
       </c>
     </row>
